--- a/examples/GalacticSoup/requirements/StakeholderNeeds.xlsx
+++ b/examples/GalacticSoup/requirements/StakeholderNeeds.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Facility may be deployed on any of a diverse set of worlds.</t>
+  </si>
+  <si>
+    <t>DerivedFrom</t>
   </si>
 </sst>
 </file>
@@ -166,13 +169,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="true"/>
     <col min="2" max="2" width="21.77734375" customWidth="true"/>
     <col min="3" max="3" width="65.21875" customWidth="true"/>
     <col min="4" max="4" width="40.21875" customWidth="true"/>
+    <col min="5" max="5" width="11.44140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -188,6 +192,9 @@
       <c r="D1" s="0" t="s">
         <v>27</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -202,6 +209,7 @@
       <c r="D2" s="0" t="s">
         <v>28</v>
       </c>
+      <c r="E2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -216,6 +224,7 @@
       <c r="D3" s="0" t="s">
         <v>29</v>
       </c>
+      <c r="E3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -230,6 +239,7 @@
       <c r="D4" s="0" t="s">
         <v>30</v>
       </c>
+      <c r="E4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -244,6 +254,7 @@
       <c r="D5" s="0" t="s">
         <v>31</v>
       </c>
+      <c r="E5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -258,6 +269,7 @@
       <c r="D6" s="0" t="s">
         <v>32</v>
       </c>
+      <c r="E6" s="0"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -272,6 +284,7 @@
       <c r="D7" s="0" t="s">
         <v>33</v>
       </c>
+      <c r="E7" s="0"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -286,6 +299,7 @@
       <c r="D8" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -300,6 +314,7 @@
       <c r="D9" s="0" t="s">
         <v>35</v>
       </c>
+      <c r="E9" s="0"/>
     </row>
   </sheetData>
 </worksheet>

--- a/examples/GalacticSoup/requirements/StakeholderNeeds.xlsx
+++ b/examples/GalacticSoup/requirements/StakeholderNeeds.xlsx
@@ -1,19 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MATLAB_Projects\Playground\galacticSoupKitchen\matlab-mbse-skills\examples\GalacticSoup\requirements\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06DF687-1406-411E-A63F-CCFB93522CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="672" yWindow="24" windowWidth="21492" windowHeight="9552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -124,16 +144,110 @@
   </si>
   <si>
     <t>DerivedFrom</t>
+  </si>
+  <si>
+    <t>SN-GS-009</t>
+  </si>
+  <si>
+    <t>SN-GS-010</t>
+  </si>
+  <si>
+    <t>SN-GS-011</t>
+  </si>
+  <si>
+    <t>SN-GS-012</t>
+  </si>
+  <si>
+    <t>Delivery fleet support</t>
+  </si>
+  <si>
+    <t>Ingredient Storage</t>
+  </si>
+  <si>
+    <t>Kitchen shall store a variety of delivered ingredients under appropriate temperature and handling conditions.</t>
+  </si>
+  <si>
+    <t>Need safe, flexible storage of both perishable and shelf-stable ingredients.</t>
+  </si>
+  <si>
+    <t>Cooking infrastructure</t>
+  </si>
+  <si>
+    <t>Kitchen shall include cooking infrastructure capable of producing soup at required production rates.</t>
+  </si>
+  <si>
+    <t>Throughput targets cannot be met without sufficient cooking capacity matched to demand.</t>
+  </si>
+  <si>
+    <t>Internal material transport</t>
+  </si>
+  <si>
+    <t>Kitchen shall transport ingredients and products internally between receiving, storage, cooking, packaging, and delivery areas.</t>
+  </si>
+  <si>
+    <t>Required to meet throughput targets.</t>
+  </si>
+  <si>
+    <t>Kitchen shall support a fleet of delivery rockets for transporting finished soup to customers and receiving inbound deliveries.</t>
+  </si>
+  <si>
+    <t>Dedicated infrastructure required for frequent launch, landing, loading, and refueling operations.</t>
+  </si>
+  <si>
+    <t>SN-GS-013</t>
+  </si>
+  <si>
+    <t>SN-GS-014</t>
+  </si>
+  <si>
+    <t>SN-GS-015</t>
+  </si>
+  <si>
+    <t>Operational lifecycle</t>
+  </si>
+  <si>
+    <t>Kitchen shall support startup, steady operation, and shutdown across its deployment lifecycle.</t>
+  </si>
+  <si>
+    <t>System must operate safely outside of nominal steady‑state conditions.</t>
+  </si>
+  <si>
+    <t>Fault tolerance</t>
+  </si>
+  <si>
+    <t>Kitchen shall continue operating or degrade safely in the presence of faults.</t>
+  </si>
+  <si>
+    <t>Production continuity and safety must be maintained with minimal crew intervention.</t>
+  </si>
+  <si>
+    <t>System coordination</t>
+  </si>
+  <si>
+    <t>Kitchen shall coordinate cooking, packaging, storage, and transport activities to meet operational goals.</t>
+  </si>
+  <si>
+    <t>High automation requires integrated system‑level control.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,7 +258,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -152,170 +266,586 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" customWidth="true"/>
-    <col min="2" max="2" width="21.77734375" customWidth="true"/>
-    <col min="3" max="3" width="65.21875" customWidth="true"/>
-    <col min="4" max="4" width="40.21875" customWidth="true"/>
-    <col min="5" max="5" width="11.44140625" customWidth="true"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" customWidth="1"/>
+    <col min="3" max="3" width="102.33203125" customWidth="1"/>
+    <col min="4" max="4" width="40.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="0"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="0"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="0"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="0"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="0"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>